--- a/地图数据/LINKDATA_177-黄巾.xlsx
+++ b/地图数据/LINKDATA_177-黄巾.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R129"/>
+  <dimension ref="A1:Q129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,85 +440,76 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>高度类型</t>
+          <t>0高度类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>区域x坐标</t>
+          <t>1区域x坐标</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>区域y坐标</t>
+          <t>2区域y坐标</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>事件影响编号</t>
+          <t>3事件影响编号</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>地形类型</t>
+          <t>4地形类型</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>5未知</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
+          <t>6未知</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr"/>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>连通区域0</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>连通区域0</t>
+          <t>连通区域1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>连通区域1</t>
+          <t>连通区域2</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>连通区域2</t>
+          <t>连通区域3</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>连通区域3</t>
+          <t>连通区域4</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>连通区域4</t>
+          <t>连通区域5</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>连通区域5</t>
+          <t>连通区域6</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>连通区域6</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>连通区域7</t>
         </is>
@@ -565,16 +556,8 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -582,7 +565,6 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -625,28 +607,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>38,02,02</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,28 +662,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>1c,02,02</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,28 +717,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>4b,02,02</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,28 +772,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>20,02,02</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -881,28 +827,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
           <t>24,02,02</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -945,28 +882,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
           <t>2a,02,02</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1009,44 +937,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3b,02,02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3b,02,02</t>
+          <t>2f,00,02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2f,00,02</t>
+          <t>3d,00,02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3d,00,02</t>
+          <t>3c,02,02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3c,02,02</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
           <t>1e,02,02</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1089,36 +1008,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4c,02,02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4c,02,02</t>
+          <t>4d,02,02</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4d,02,02</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
           <t>4f,02,02</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1161,40 +1071,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1d,02,02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1d,02,02</t>
+          <t>3f,00,02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3f,00,02</t>
+          <t>3e,02,02</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3e,02,02</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
           <t>20,02,02</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1237,48 +1138,39 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1e,02,02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1e,02,02</t>
+          <t>1f,02,02</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1f,02,02</t>
+          <t>56,02,02</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>56,02,02</t>
+          <t>34,02,02</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>34,02,02</t>
+          <t>41,00,02</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>41,00,02</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
           <t>40,02,02</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1321,44 +1213,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21,00,02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21,00,02</t>
+          <t>43,00,02</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>43,00,02</t>
+          <t>48,02,02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>48,02,02</t>
+          <t>42,02,02</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42,02,02</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
           <t>23,02,02</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1401,44 +1284,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2b,02,02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2b,02,02</t>
+          <t>45,00,02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>45,00,02</t>
+          <t>44,02,02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>44,02,02</t>
+          <t>29,02,02</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29,02,02</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
           <t>2c,02,02</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1481,44 +1355,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27,02,02</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27,02,02</t>
+          <t>28,02,02</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28,02,02</t>
+          <t>47,00,02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47,00,02</t>
+          <t>46,02,02</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46,02,02</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
           <t>57,02,02</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1561,32 +1426,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18,02,02</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18,02,02</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
           <t>52,02,02</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1629,32 +1485,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19,02,02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19,02,02</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
           <t>1a,02,02</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1697,32 +1544,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1a,02,02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1a,02,02</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
           <t>1b,02,02</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1765,32 +1603,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1b,02,02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1b,02,02</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
           <t>1c,02,02</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1833,32 +1662,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2a,02,02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2a,02,02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
           <t>26,02,02</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1901,36 +1721,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1e,02,02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1e,02,02</t>
+          <t>48,02,02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>48,02,02</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
           <t>14,02,02</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1973,40 +1784,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34,02,02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34,02,02</t>
+          <t>13,02,02</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>13,02,02</t>
+          <t>15,02,02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>15,02,02</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
           <t>37,02,02</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2049,32 +1851,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29,02,02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>29,02,02</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
           <t>14,02,02</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2117,36 +1910,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20,02,02</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20,02,02</t>
+          <t>2b,00,02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2b,00,02</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
           <t>29,00,02</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2189,36 +1973,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2f,02,02</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2f,02,02</t>
+          <t>52,02,02</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>52,02,02</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
           <t>1e,02,00</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2261,32 +2036,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30,02,02</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30,02,02</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
           <t>0e,02,02</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2329,32 +2095,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31,02,02</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31,02,02</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
           <t>0f,02,02</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2397,40 +2154,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0f,02,02</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0f,02,02</t>
+          <t>10,02,02</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10,02,02</t>
+          <t>51,02,02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>51,02,02</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
           <t>1f,02,00</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2473,32 +2221,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11,02,02</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11,02,02</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
           <t>10,02,02</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2541,36 +2280,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>02,02,02</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02,02,02</t>
+          <t>11,02,02</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>11,02,02</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
           <t>33,02,02</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2613,32 +2343,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33,02,02</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>33,02,02</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
           <t>09,02,02</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2681,52 +2402,43 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17,00,02</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17,00,02</t>
+          <t>1f,02,02</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1f,02,02</t>
+          <t>07,02,02</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>07,02,02</t>
+          <t>4b,02,02</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4b,02,02</t>
+          <t>13,02,02</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>13,02,02</t>
+          <t>0a,02,02</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0a,02,02</t>
+          <t>2e,02,02</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
-        <is>
-          <t>2e,02,02</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
         <is>
           <t>21,00,02</t>
         </is>
@@ -2773,48 +2485,39 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1a,00,02</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1a,00,02</t>
+          <t>55,02,02</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>55,02,02</t>
+          <t>53,02,02</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>53,02,02</t>
+          <t>1e,02,02</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1e,02,02</t>
+          <t>20,02,02</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20,02,02</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
           <t>0a,02,02</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2857,48 +2560,39 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1f,02,02</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1f,02,02</t>
+          <t>09,02,02</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>09,02,02</t>
+          <t>04,02,02</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>04,02,02</t>
+          <t>35,02,02</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>35,02,02</t>
+          <t>16,02,02</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>16,02,02</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
           <t>2b,00,02</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2941,44 +2635,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2e,02,00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2e,02,00</t>
+          <t>1e,02,00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1e,02,00</t>
+          <t>48,02,00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>48,02,00</t>
+          <t>0b,02,00</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0b,02,00</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
           <t>22,02,02</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3021,32 +2706,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21,02,02</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21,02,02</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
           <t>49,02,02</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3089,36 +2765,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0b,02,02</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0b,02,02</t>
+          <t>24,02,02</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>24,02,02</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
           <t>49,02,02</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3161,40 +2828,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25,02,02</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>25,02,02</t>
+          <t>27,02,02</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>27,02,02</t>
+          <t>23,02,02</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>23,02,02</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
           <t>05,02,02</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3237,48 +2895,39 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24,02,02</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>24,02,02</t>
+          <t>37,00,02</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>37,00,02</t>
+          <t>26,02,02</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>26,02,02</t>
+          <t>54,00,02</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>54,00,02</t>
+          <t>27,00,02</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>27,00,02</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
           <t>28,00,02</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3321,40 +2970,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25,02,02</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25,02,02</t>
+          <t>29,00,02</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>29,00,02</t>
+          <t>36,02,02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>36,02,02</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
           <t>12,02,02</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3397,40 +3037,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24,02,02</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>24,02,02</t>
+          <t>25,02,00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>25,02,00</t>
+          <t>28,02,02</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>28,02,02</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
           <t>0d,02,02</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3473,44 +3104,35 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54,02,02</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>54,02,02</t>
+          <t>27,02,02</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>27,02,02</t>
+          <t>25,02,00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>25,02,00</t>
+          <t>36,02,02</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>36,02,02</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
           <t>0d,02,02</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3553,40 +3175,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15,02,02</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>15,02,02</t>
+          <t>16,02,00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>16,02,00</t>
+          <t>26,02,00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>26,02,00</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
           <t>0c,02,02</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3629,36 +3242,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12,02,02</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>12,02,02</t>
+          <t>2c,02,02</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2c,02,02</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
           <t>06,02,02</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3701,40 +3305,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35,02,02</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>35,02,02</t>
+          <t>20,02,00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>20,02,00</t>
+          <t>16,02,00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16,02,00</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
           <t>0c,02,02</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3777,32 +3372,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0c,02,02</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0c,02,02</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
           <t>2a,02,02</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3845,28 +3431,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
           <t>38,02,02</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3909,36 +3486,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4b,02,02</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4b,02,02</t>
+          <t>1e,02,02</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1e,02,02</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
           <t>21,00,02</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3981,40 +3549,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39,02,02</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>39,02,02</t>
+          <t>3b,02,00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3b,02,00</t>
+          <t>07,02,00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>07,02,00</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
           <t>17,02,02</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4057,32 +3616,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4e,02,02</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4e,02,02</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
           <t>18,02,02</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4125,32 +3675,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4e,02,02</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4e,02,02</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
           <t>19,02,02</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4193,32 +3734,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4f,02,02</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4f,02,02</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
           <t>53,02,02</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4261,32 +3793,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1c,02,02</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1c,02,02</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
           <t>1d,02,02</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4329,32 +3852,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0a,02,02</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0a,02,02</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
           <t>14,02,02</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4397,32 +3911,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20,02,02</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>20,02,02</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
           <t>2b,02,02</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4465,32 +3970,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28,02,02</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>28,02,02</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
           <t>26,02,02</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4533,36 +4029,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14,02,02</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>14,02,02</t>
+          <t>25,02,00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>25,02,00</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
           <t>54,02,02</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4605,40 +4092,31 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2d,02,02</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2d,02,02</t>
+          <t>01,02,02</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>01,02,02</t>
+          <t>3a,02,02</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>3a,02,02</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
           <t>39,02,02</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4681,32 +4159,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38,02,02</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>38,02,02</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
           <t>2f,02,02</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4749,32 +4218,23 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38,02,02</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>38,02,02</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
           <t>3b,02,02</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4817,36 +4277,27 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3a,02,02</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>3a,02,02</t>
+          <t>2f,00,02</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2f,00,02</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
           <t>07,02,02</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4889,28 +4340,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
           <t>07,02,02</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4953,28 +4395,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
           <t>07,02,00</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5017,28 +4450,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
           <t>09,02,02</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5081,28 +4505,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
           <t>09,02,00</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5145,28 +4560,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
           <t>0a,02,02</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5209,28 +4615,19 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
           <t>0a,02,00</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5273,28 +4670,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
           <t>0b,02,02</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5337,28 +4725,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
           <t>0b,02,00</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5401,28 +4780,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
           <t>0c,02,02</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5465,28 +4835,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
           <t>0c,02,00</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5529,28 +4890,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
           <t>0d,02,02</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5593,28 +4945,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
           <t>0d,02,00</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5657,36 +5000,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21,00,02</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>21,00,02</t>
+          <t>13,02,02</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>13,02,02</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
           <t>0b,02,02</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5729,32 +5063,23 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23,02,02</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>23,02,02</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
           <t>22,02,02</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5797,28 +5122,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
           <t>4e,02,02</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5861,36 +5177,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1e,02,02</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1e,02,02</t>
+          <t>03,02,02</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>03,02,02</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
           <t>2e,02,02</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5933,40 +5240,31 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4e,02,02</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4e,02,02</t>
+          <t>4d,02,02</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>4d,02,02</t>
+          <t>08,02,02</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>08,02,02</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
           <t>4f,02,02</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6009,40 +5307,31 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4e,02,02</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4e,02,02</t>
+          <t>4c,02,02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>4c,02,02</t>
+          <t>08,02,02</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>08,02,02</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
           <t>4f,02,02</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6085,44 +5374,35 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4a,02,02</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4a,02,02</t>
+          <t>30,02,02</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>30,02,02</t>
+          <t>4c,02,02</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>4c,02,02</t>
+          <t>4d,02,02</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>4d,02,02</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
           <t>31,02,02</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6165,40 +5445,31 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4c,02,02</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4c,02,02</t>
+          <t>4d,02,02</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>4d,02,02</t>
+          <t>08,02,02</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>08,02,02</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
           <t>32,02,02</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6241,28 +5512,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
           <t>52,02,02</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6305,28 +5567,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
           <t>1a,02,02</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6369,36 +5622,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0e,02,02</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0e,02,02</t>
+          <t>17,02,02</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>17,02,02</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
           <t>50,02,02</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6441,32 +5685,23 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32,02,02</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>32,02,02</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
           <t>1f,02,02</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6509,36 +5744,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>37,02,02</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>37,02,02</t>
+          <t>25,02,00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>25,02,00</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
           <t>28,02,02</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6581,28 +5807,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
           <t>1f,02,02</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6645,28 +5862,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
           <t>0a,02,02</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6709,28 +5917,19 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
           <t>0d,02,02</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6773,16 +5972,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
@@ -6790,7 +5981,6 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6833,16 +6023,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -6850,7 +6032,6 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6893,16 +6074,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -6910,7 +6083,6 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6953,16 +6125,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
@@ -6970,7 +6134,6 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7013,16 +6176,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
@@ -7030,7 +6185,6 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7073,16 +6227,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -7090,7 +6236,6 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7133,16 +6278,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
@@ -7150,7 +6287,6 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7193,16 +6329,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
@@ -7210,7 +6338,6 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7253,16 +6380,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
@@ -7270,7 +6389,6 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7313,16 +6431,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -7330,7 +6440,6 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7373,16 +6482,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
@@ -7390,7 +6491,6 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7433,16 +6533,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
@@ -7450,7 +6542,6 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7493,16 +6584,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
@@ -7510,7 +6593,6 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7553,16 +6635,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
@@ -7570,7 +6644,6 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7613,16 +6686,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
@@ -7630,7 +6695,6 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7673,16 +6737,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
@@ -7690,7 +6746,6 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7733,16 +6788,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
@@ -7750,7 +6797,6 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7793,16 +6839,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
@@ -7810,7 +6848,6 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7853,16 +6890,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
@@ -7870,7 +6899,6 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7913,16 +6941,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
@@ -7930,7 +6950,6 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7973,16 +6992,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
@@ -7990,7 +7001,6 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8033,16 +7043,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
@@ -8050,7 +7052,6 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8093,16 +7094,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
@@ -8110,7 +7103,6 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8153,16 +7145,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
@@ -8170,7 +7154,6 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8213,16 +7196,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
@@ -8230,7 +7205,6 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8273,16 +7247,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
@@ -8290,7 +7256,6 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8333,16 +7298,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
@@ -8350,7 +7307,6 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8393,16 +7349,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
@@ -8410,7 +7358,6 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8453,16 +7400,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
@@ -8470,7 +7409,6 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8513,16 +7451,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
@@ -8530,7 +7460,6 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8573,16 +7502,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
@@ -8590,7 +7511,6 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8633,16 +7553,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
@@ -8650,7 +7562,6 @@
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8693,16 +7604,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
@@ -8710,7 +7613,6 @@
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8753,16 +7655,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
@@ -8770,7 +7664,6 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8813,16 +7706,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
@@ -8830,7 +7715,6 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8873,16 +7757,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
@@ -8890,7 +7766,6 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8933,16 +7808,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
@@ -8950,7 +7817,6 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8993,16 +7859,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
@@ -9010,7 +7868,6 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9053,16 +7910,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
@@ -9070,7 +7919,6 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9113,16 +7961,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
@@ -9130,7 +7970,6 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -61002,17 +59841,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>据点类型</t>
+          <t>0据点类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>据点所在区域编号</t>
+          <t>1据点所在区域编号</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2未知</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr"/>
@@ -61023,7 +59862,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>刷兵点所在区域编号</t>
+          <t>0刷兵点所在区域编号</t>
         </is>
       </c>
     </row>
